--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.06536</v>
+        <v>16.79528</v>
       </c>
       <c r="D2" t="n">
-        <v>16.47137</v>
+        <v>16.36959</v>
       </c>
       <c r="E2" t="n">
-        <v>16.62011</v>
+        <v>16.4963</v>
       </c>
       <c r="F2" t="n">
-        <v>42.65844</v>
+        <v>42.79078</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05053</v>
+        <v>0.04884</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84308</v>
+        <v>1.79694</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.53326</v>
+        <v>16.99072</v>
       </c>
       <c r="D3" t="n">
-        <v>16.73731</v>
+        <v>16.65968</v>
       </c>
       <c r="E3" t="n">
-        <v>16.94199</v>
+        <v>16.7446</v>
       </c>
       <c r="F3" t="n">
-        <v>41.89249</v>
+        <v>42.76645</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0507</v>
+        <v>0.05014</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8099</v>
+        <v>1.80359</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.75284</v>
+        <v>17.03298</v>
       </c>
       <c r="D4" t="n">
-        <v>16.7179</v>
+        <v>16.74656</v>
       </c>
       <c r="E4" t="n">
-        <v>16.47049</v>
+        <v>16.80033</v>
       </c>
       <c r="F4" t="n">
-        <v>42.49069</v>
+        <v>42.69841</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05092</v>
+        <v>0.05103</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85016</v>
+        <v>1.8329</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.69958</v>
+        <v>16.8973</v>
       </c>
       <c r="D6" t="n">
-        <v>15.69572</v>
+        <v>15.73934</v>
       </c>
       <c r="E6" t="n">
-        <v>16.29659</v>
+        <v>16.39694</v>
       </c>
       <c r="F6" t="n">
-        <v>21.54233</v>
+        <v>21.25746</v>
       </c>
       <c r="G6" t="n">
-        <v>34.23676</v>
+        <v>34.46618</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.55335</v>
+        <v>16.84468</v>
       </c>
       <c r="D7" t="n">
-        <v>15.47851</v>
+        <v>16.02856</v>
       </c>
       <c r="E7" t="n">
-        <v>15.97871</v>
+        <v>16.2848</v>
       </c>
       <c r="F7" t="n">
-        <v>21.84617</v>
+        <v>22.2321</v>
       </c>
       <c r="G7" t="n">
-        <v>34.16072</v>
+        <v>34.03149</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.457</v>
+        <v>16.8625</v>
       </c>
       <c r="D8" t="n">
-        <v>15.3771</v>
+        <v>15.85019</v>
       </c>
       <c r="E8" t="n">
-        <v>16.36895</v>
+        <v>16.36661</v>
       </c>
       <c r="F8" t="n">
-        <v>21.76169</v>
+        <v>21.61044</v>
       </c>
       <c r="G8" t="n">
-        <v>33.73172</v>
+        <v>34.11097</v>
       </c>
     </row>
   </sheetData>
